--- a/Examples/GroupDocs.Assembly.Examples.Java/Data/Output/Spreadsheet Reports/Dynamic Chart Series Color.xlsx
+++ b/Examples/GroupDocs.Assembly.Examples.Java/Data/Output/Spreadsheet Reports/Dynamic Chart Series Color.xlsx
@@ -308,11 +308,11 @@
         </c:dLbls>
         <c:overlap val="-27"/>
         <c:gapWidth val="219"/>
-        <c:axId val="835384913"/>
-        <c:axId val="769717219"/>
+        <c:axId val="795528652"/>
+        <c:axId val="1240784398"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="835384913"/>
+        <c:axId val="795528652"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -355,14 +355,14 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="769717219"/>
+        <c:crossAx val="1240784398"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="769717219"/>
+        <c:axId val="1240784398"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -413,7 +413,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="835384913"/>
+        <c:crossAx val="795528652"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>

--- a/Examples/GroupDocs.Assembly.Examples.Java/Data/Output/Spreadsheet Reports/Dynamic Chart Series Color.xlsx
+++ b/Examples/GroupDocs.Assembly.Examples.Java/Data/Output/Spreadsheet Reports/Dynamic Chart Series Color.xlsx
@@ -308,11 +308,11 @@
         </c:dLbls>
         <c:overlap val="-27"/>
         <c:gapWidth val="219"/>
-        <c:axId val="795528652"/>
-        <c:axId val="1240784398"/>
+        <c:axId val="1787140327"/>
+        <c:axId val="1582068972"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="795528652"/>
+        <c:axId val="1787140327"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -355,14 +355,14 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1240784398"/>
+        <c:crossAx val="1582068972"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="1240784398"/>
+        <c:axId val="1582068972"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -413,7 +413,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="795528652"/>
+        <c:crossAx val="1787140327"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>

--- a/Examples/GroupDocs.Assembly.Examples.Java/Data/Output/Spreadsheet Reports/Dynamic Chart Series Color.xlsx
+++ b/Examples/GroupDocs.Assembly.Examples.Java/Data/Output/Spreadsheet Reports/Dynamic Chart Series Color.xlsx
@@ -308,11 +308,11 @@
         </c:dLbls>
         <c:overlap val="-27"/>
         <c:gapWidth val="219"/>
+        <c:axId val="63010542"/>
         <c:axId val="1787140327"/>
-        <c:axId val="1582068972"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="1787140327"/>
+        <c:axId val="63010542"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -355,14 +355,14 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1582068972"/>
+        <c:crossAx val="1787140327"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="1582068972"/>
+        <c:axId val="1787140327"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -413,7 +413,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1787140327"/>
+        <c:crossAx val="63010542"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
